--- a/public/samples/ko/sample-group.xlsx
+++ b/public/samples/ko/sample-group.xlsx
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -468,6 +468,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -483,9 +486,12 @@
         <v>학업 성취도</v>
       </c>
       <c r="E2" s="2" t="str">
+        <v>수학 수준</v>
+      </c>
+      <c r="F2" s="2" t="str">
         <v>리더십</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="G2" s="2" t="str">
         <v>이전 모둠</v>
       </c>
     </row>
@@ -502,10 +508,13 @@
       <c r="D3" s="2">
         <v>76</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F3" s="2">
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="2">
         <v>2</v>
       </c>
     </row>
@@ -514,19 +523,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>강민준</v>
+        <v>장민준</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D4" s="2">
-        <v>62</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F4" s="2">
-        <v>3</v>
+        <v>70</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -534,18 +546,21 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>홍지우</v>
+        <v>오지우</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D5" s="2">
-        <v>74</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F5" s="2">
+        <v>83</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="2">
         <v>4</v>
       </c>
     </row>
@@ -554,18 +569,21 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>장서준</v>
+        <v>윤서준</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D6" s="2">
-        <v>81</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F6" s="2">
+        <v>65</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G6" s="2">
         <v>1</v>
       </c>
     </row>
@@ -574,18 +592,21 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>오서윤</v>
+        <v>장서윤</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D7" s="2">
-        <v>78</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="2">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -594,18 +615,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>장도윤</v>
+        <v>류도윤</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D8" s="2">
-        <v>74</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F8" s="2">
+        <v>73</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="2">
         <v>3</v>
       </c>
     </row>
@@ -614,19 +638,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>류하은</v>
+        <v>서하은</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D9" s="2">
-        <v>73</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F9" s="2">
-        <v>3</v>
+        <v>88</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -634,19 +661,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>김예준</v>
+        <v>홍예준</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D10" s="2">
-        <v>88</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F10" s="2">
-        <v>2</v>
+        <v>77</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -654,19 +684,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>신민서</v>
+        <v>오민서</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D11" s="2">
-        <v>86</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F11" s="2">
-        <v>4</v>
+        <v>71</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -674,18 +707,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>최시우</v>
+        <v>임시우</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D12" s="2">
-        <v>86</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F12" s="2">
+        <v>80</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G12" s="2">
         <v>2</v>
       </c>
     </row>
@@ -694,19 +730,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>서지유</v>
+        <v>임지유</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D13" s="2">
-        <v>84</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
+        <v>86</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -714,19 +753,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>강하준</v>
+        <v>윤하준</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D14" s="2">
-        <v>72</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F14" s="2">
-        <v>6</v>
+        <v>63</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +776,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>최윤서</v>
+        <v>송윤서</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>여</v>
@@ -742,11 +784,14 @@
       <c r="D15" s="2">
         <v>80</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F15" s="2">
-        <v>3</v>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -754,19 +799,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>윤주원</v>
+        <v>황주원</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D16" s="2">
-        <v>71</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
+        <v>87</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -774,18 +822,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>한채원</v>
+        <v>임채원</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D17" s="2">
-        <v>80</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F17" s="2">
+        <v>82</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2">
         <v>5</v>
       </c>
     </row>
@@ -794,18 +845,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>정지호</v>
+        <v>조지호</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D18" s="2">
-        <v>88</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F18" s="2">
+        <v>70</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2">
         <v>1</v>
       </c>
     </row>
@@ -814,19 +868,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>이수아</v>
+        <v>윤수아</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D19" s="2">
-        <v>72</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F19" s="2">
-        <v>5</v>
+        <v>84</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -834,7 +891,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>오지후</v>
+        <v>조지후</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>남</v>
@@ -842,11 +899,14 @@
       <c r="D20" s="2">
         <v>80</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F20" s="2">
-        <v>3</v>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -854,18 +914,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>오지민</v>
+        <v>송지민</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D21" s="2">
-        <v>73</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F21" s="2">
+        <v>85</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="2">
         <v>5</v>
       </c>
     </row>
@@ -874,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>황준우</v>
+        <v>윤준우</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>남</v>
@@ -882,11 +945,14 @@
       <c r="D22" s="2">
         <v>81</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F22" s="2">
-        <v>3</v>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -894,19 +960,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>조예은</v>
+        <v>윤예은</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D23" s="2">
-        <v>76</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F23" s="2">
-        <v>5</v>
+        <v>75</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +983,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>신건우</v>
+        <v>홍건우</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D24" s="2">
-        <v>85</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F24" s="2">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -934,19 +1006,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>강다은</v>
+        <v>김다은</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D25" s="2">
-        <v>86</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="2">
-        <v>2</v>
+        <v>91</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -954,19 +1029,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>정우진</v>
+        <v>강우진</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D26" s="2">
-        <v>64</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F26" s="2">
-        <v>5</v>
+        <v>73</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +1052,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>홍하린</v>
+        <v>신하린</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D27" s="2">
-        <v>75</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F27" s="2">
-        <v>3</v>
+        <v>72</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G27" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -994,19 +1075,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>류선우</v>
+        <v>김선우</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D28" s="2">
-        <v>71</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F28" s="2">
-        <v>5</v>
+        <v>81</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1014,18 +1098,21 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>김소율</v>
+        <v>신소율</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D29" s="2">
-        <v>73</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F29" s="2">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G29" s="2">
         <v>1</v>
       </c>
     </row>
@@ -1034,19 +1121,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>강현우</v>
+        <v>윤현우</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D30" s="2">
-        <v>78</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F30" s="2">
-        <v>3</v>
+        <v>79</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G30" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1054,19 +1144,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>강유나</v>
+        <v>조유나</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D31" s="2">
-        <v>72</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="2">
-        <v>2</v>
+        <v>79</v>
+      </c>
+      <c r="E31" s="2">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G31" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -1074,24 +1167,27 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>황연우</v>
+        <v>오연우</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D32" s="2">
-        <v>76</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F32" s="2">
-        <v>3</v>
+        <v>62</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1112,37 +1208,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/ko/sample-group.xlsx
+++ b/public/samples/ko/sample-group.xlsx
@@ -7,6 +7,7 @@
     <sheet name="학생 명단" sheetId="2" r:id="rId2"/>
     <sheet name="같은 반 배정" sheetId="3" r:id="rId3"/>
     <sheet name="분리 배정" sheetId="4" r:id="rId4"/>
+    <sheet name="항목" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -1246,4 +1247,90 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>종류</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>선택지</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>성별</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>남</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>여</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>학업 성취도</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>숫자</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>수학 수준</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>정도</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>리더십</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>이전 모둠</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/ko/sample-group.xlsx
+++ b/public/samples/ko/sample-group.xlsx
@@ -7,6 +7,7 @@
     <sheet name="학생 명단" sheetId="2" r:id="rId2"/>
     <sheet name="같은 반 배정" sheetId="3" r:id="rId3"/>
     <sheet name="분리 배정" sheetId="4" r:id="rId4"/>
+    <sheet name="항목" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -447,7 +448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -468,6 +469,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -483,9 +487,12 @@
         <v>학업 성취도</v>
       </c>
       <c r="E2" s="2" t="str">
+        <v>수학 수준</v>
+      </c>
+      <c r="F2" s="2" t="str">
         <v>리더십</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="G2" s="2" t="str">
         <v>이전 모둠</v>
       </c>
     </row>
@@ -502,10 +509,13 @@
       <c r="D3" s="2">
         <v>76</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F3" s="2">
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="2">
         <v>2</v>
       </c>
     </row>
@@ -514,19 +524,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>강민준</v>
+        <v>장민준</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D4" s="2">
-        <v>62</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F4" s="2">
-        <v>3</v>
+        <v>70</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -534,18 +547,21 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>홍지우</v>
+        <v>오지우</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D5" s="2">
-        <v>74</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F5" s="2">
+        <v>83</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="2">
         <v>4</v>
       </c>
     </row>
@@ -554,18 +570,21 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>장서준</v>
+        <v>윤서준</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D6" s="2">
-        <v>81</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F6" s="2">
+        <v>65</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G6" s="2">
         <v>1</v>
       </c>
     </row>
@@ -574,18 +593,21 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>오서윤</v>
+        <v>장서윤</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D7" s="2">
-        <v>78</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="2">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -594,18 +616,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>장도윤</v>
+        <v>류도윤</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D8" s="2">
-        <v>74</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F8" s="2">
+        <v>73</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="2">
         <v>3</v>
       </c>
     </row>
@@ -614,19 +639,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>류하은</v>
+        <v>서하은</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D9" s="2">
-        <v>73</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F9" s="2">
-        <v>3</v>
+        <v>88</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -634,19 +662,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>김예준</v>
+        <v>홍예준</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D10" s="2">
-        <v>88</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F10" s="2">
-        <v>2</v>
+        <v>77</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -654,19 +685,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>신민서</v>
+        <v>오민서</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D11" s="2">
-        <v>86</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F11" s="2">
-        <v>4</v>
+        <v>71</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -674,18 +708,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>최시우</v>
+        <v>임시우</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D12" s="2">
-        <v>86</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F12" s="2">
+        <v>80</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G12" s="2">
         <v>2</v>
       </c>
     </row>
@@ -694,19 +731,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>서지유</v>
+        <v>임지유</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D13" s="2">
-        <v>84</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
+        <v>86</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -714,19 +754,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>강하준</v>
+        <v>윤하준</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D14" s="2">
-        <v>72</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F14" s="2">
-        <v>6</v>
+        <v>63</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +777,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>최윤서</v>
+        <v>송윤서</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>여</v>
@@ -742,11 +785,14 @@
       <c r="D15" s="2">
         <v>80</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F15" s="2">
-        <v>3</v>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -754,19 +800,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>윤주원</v>
+        <v>황주원</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D16" s="2">
-        <v>71</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
+        <v>87</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -774,18 +823,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>한채원</v>
+        <v>임채원</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D17" s="2">
-        <v>80</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F17" s="2">
+        <v>82</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2">
         <v>5</v>
       </c>
     </row>
@@ -794,18 +846,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>정지호</v>
+        <v>조지호</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D18" s="2">
-        <v>88</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F18" s="2">
+        <v>70</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2">
         <v>1</v>
       </c>
     </row>
@@ -814,19 +869,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>이수아</v>
+        <v>윤수아</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D19" s="2">
-        <v>72</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F19" s="2">
-        <v>5</v>
+        <v>84</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -834,7 +892,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>오지후</v>
+        <v>조지후</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>남</v>
@@ -842,11 +900,14 @@
       <c r="D20" s="2">
         <v>80</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F20" s="2">
-        <v>3</v>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -854,18 +915,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>오지민</v>
+        <v>송지민</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D21" s="2">
-        <v>73</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F21" s="2">
+        <v>85</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="2">
         <v>5</v>
       </c>
     </row>
@@ -874,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>황준우</v>
+        <v>윤준우</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>남</v>
@@ -882,11 +946,14 @@
       <c r="D22" s="2">
         <v>81</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F22" s="2">
-        <v>3</v>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -894,19 +961,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>조예은</v>
+        <v>윤예은</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D23" s="2">
-        <v>76</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F23" s="2">
-        <v>5</v>
+        <v>75</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +984,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>신건우</v>
+        <v>홍건우</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D24" s="2">
-        <v>85</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F24" s="2">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -934,19 +1007,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>강다은</v>
+        <v>김다은</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D25" s="2">
-        <v>86</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="2">
-        <v>2</v>
+        <v>91</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -954,19 +1030,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>정우진</v>
+        <v>강우진</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D26" s="2">
-        <v>64</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F26" s="2">
-        <v>5</v>
+        <v>73</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +1053,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>홍하린</v>
+        <v>신하린</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D27" s="2">
-        <v>75</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F27" s="2">
-        <v>3</v>
+        <v>72</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G27" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -994,19 +1076,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>류선우</v>
+        <v>김선우</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D28" s="2">
-        <v>71</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F28" s="2">
-        <v>5</v>
+        <v>81</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1014,18 +1099,21 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>김소율</v>
+        <v>신소율</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D29" s="2">
-        <v>73</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F29" s="2">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G29" s="2">
         <v>1</v>
       </c>
     </row>
@@ -1034,19 +1122,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>강현우</v>
+        <v>윤현우</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D30" s="2">
-        <v>78</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F30" s="2">
-        <v>3</v>
+        <v>79</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G30" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1054,19 +1145,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>강유나</v>
+        <v>조유나</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D31" s="2">
-        <v>72</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="2">
-        <v>2</v>
+        <v>79</v>
+      </c>
+      <c r="E31" s="2">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G31" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -1074,24 +1168,27 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>황연우</v>
+        <v>오연우</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D32" s="2">
-        <v>76</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F32" s="2">
-        <v>3</v>
+        <v>62</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1112,37 +1209,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1150,4 +1247,90 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>종류</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>선택지</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>성별</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>남</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>여</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>학업 성취도</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>숫자</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>수학 수준</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>정도</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>리더십</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>이전 모둠</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+  </ignoredErrors>
+</worksheet>
 </file>